--- a/data/Controle_Financeiro_Pequenas_Empresas.xlsx
+++ b/data/Controle_Financeiro_Pequenas_Empresas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\InsightFinance\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D92D141-CA76-4094-890B-EA3AF163C8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74BD5B8-1219-4288-BADA-262C95B1543E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="300" windowWidth="19290" windowHeight="10620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="300" windowWidth="19290" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendas" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,23 +178,31 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -211,28 +229,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -536,6 +569,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
@@ -545,340 +579,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>46158</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>2</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <v>3500</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="7">
         <v>7000</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>46158</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>5</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="7">
         <v>80</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="7">
         <v>400</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>46158</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="7">
         <v>1200</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="7">
         <v>1200</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1">
         <f t="shared" ref="F5:F20" si="0">D5*E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -896,181 +930,181 @@
     <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>46158</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="6">
         <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>46158</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="6">
         <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>46158</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1089,129 +1123,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2">
+      <c r="A2" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B2" s="9">
         <f>SUMIF(Vendas!G:G,"Sim",Vendas!F:F)</f>
         <v>7400</v>
       </c>
-      <c r="C2" s="2" t="e">
+      <c r="C2" s="1" t="e">
         <f>SUM(Despesas!#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="D2" s="2" t="e">
+      <c r="D2" s="1" t="e">
         <f>B2-C2</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1228,69 +1264,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="9">
         <f>SUM(Vendas!F:F)</f>
         <v>8600</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="e">
+      <c r="B3" s="1" t="e">
         <f>SUM(Despesas!#REF!)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="e">
+      <c r="B4" s="1" t="e">
         <f>B2-B3</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <f>AVERAGE(Vendas!F:F)</f>
         <v>452.63157894736844</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <f>COUNTIF(Vendas!G:G,"Não")/COUNTA(Vendas!G:G)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1309,114 +1345,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1">
         <f t="shared" ref="D2:D11" si="0">IF(B2&gt;0,C2/B2,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
